--- a/lines of best fit for smc and lmc.xlsx
+++ b/lines of best fit for smc and lmc.xlsx
@@ -8,13 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dperez/Documents/2026/Term 3/Astrophysics/GitHub/phys3116assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CE7EACA-CE1C-2D46-ACBD-DF279FC43CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E114CA41-0613-A347-97E8-9ADF48540E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39180" yWindow="3300" windowWidth="27640" windowHeight="16440" xr2:uid="{5BC30E02-4A98-3F4D-A872-EA2924F2F362}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{5BC30E02-4A98-3F4D-A872-EA2924F2F362}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$E$1</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$E$2:$E$161</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$F$1</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$F$2:$F$161</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$E$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$E$2:$E$161</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$F$1</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$F$2:$F$161</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,15 +46,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
   <si>
     <t>Fe/H</t>
   </si>
   <si>
     <t>Age</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -277,7 +284,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$12</c:f>
+              <c:f>Sheet1!$C$2:$C$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -601,7 +608,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$1</c:f>
+              <c:f>Sheet1!$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -685,7 +692,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$161</c:f>
+              <c:f>Sheet1!$F$2:$F$161</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="160"/>
@@ -1165,7 +1172,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$161</c:f>
+              <c:f>Sheet1!$E$2:$E$161</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="160"/>
@@ -1830,6 +1837,1290 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Age</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.25870122484689412"/>
+                  <c:y val="-0.13706547098279381"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$161</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="160"/>
+                <c:pt idx="0">
+                  <c:v>-1.23</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.59</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.1299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.86</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1.28</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.91</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1.01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1.21</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1.26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1.31</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.71</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.75</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1.23</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.71</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-1.3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-1.26</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-1.2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-1.43</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-1.23</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.94</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.87</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-1.23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.94</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-1.21</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-1.03</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-1.21</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-1.24</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-1.1599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-1.28</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-1.05</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-0.93</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-1.18</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-1.05</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-1.4</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-0.93</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-1.21</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-1.5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-1.26</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-1.33</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-1.31</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-0.74</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-1.23</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-1.31</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-1.29</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-0.91</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-1.27</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-1.92</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-1.23</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-1.27</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-1.48</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-0.65</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-1.23</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-0.87</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-1.45</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-0.84</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-1.1599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-1.29</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-1.26</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-1.28</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-1.39</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-0.77</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-1.31</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-1.01</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-1.34</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-1.18</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-1.21</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-1.18</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-1.21</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-1.18</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>-1.31</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>-0.84</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-1.18</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-1.23</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>-1.92</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>-1.1399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>-1.23</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>-1.34</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>-1.21</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>-1.27</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>-1.32</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>-0.66</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>-1.23</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>-1.05</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>-1.34</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>-0.96</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>-1.27</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>-1.34</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>-1.75</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>-1.22</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>-1.48</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>-0.69</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>-1.28</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>-0.96</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>-1.45</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>-1.05</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>-1.17</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>-1.29</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>-1.27</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>-1.27</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>-1.43</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>-0.64</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>-1.19</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>-1.08</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>-1.45</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>-0.91</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>-1.17</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>-1.25</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>-1.53</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>-1.18</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>-1.38</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>-0.63</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>-1.18</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>-1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>-1.29</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>-0.98</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>-1.17</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>-1.18</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>-1.1599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>-1.26</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>-1.38</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>-0.95</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>-1.06</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>-1.03</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>-0.79</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>-1.1299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>-1.08</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>-1.28</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>-1.18</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>-1.39</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>-0.85</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>-1.18</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>-1.08</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>-1.4</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>-0.91</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>-1.1599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>-1.45</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>-1.22</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>-1.17</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>-1.39</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>-0.69</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>-1.23</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>-1.08</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>-0.91</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>-1.29</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>-1.33</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>-1.18</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>-1.43</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>-0.69</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>-1.28</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>-1.3</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>-1.45</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>-1.03</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>-1.1100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>-1.22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$2:$F$161</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="160"/>
+                <c:pt idx="0">
+                  <c:v>9.5500000000000007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.08</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.73</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.74</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.04</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.56</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.93</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10.06</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.87</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.92</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.73</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6.21</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.38</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.93</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.21</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>11.72</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>9.5500000000000007</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.61</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.48</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.61</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.4400000000000004</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.56</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9.07</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8.15</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9.07</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>9.5500000000000007</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.38</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.27</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3.37</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>10.59</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>6.93</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>10.59</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>9.07</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>9.5500000000000007</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>5.26</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2.08</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>5.26</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>5.87</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2.17</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>7.32</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>13.59</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>7.32</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1.47</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.54</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>10.59</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2.08</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.26</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>8.15</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>9.07</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>9.5500000000000007</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.89</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>10.6</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2.17</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>8.15</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>6.93</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>6.93</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>4.4400000000000004</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1.85</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>3.56</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>13.59</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>9.5549999999999997</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>8.15</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>6.93</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>7.32</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>7.32</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>1.73</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>3.38</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>8.15</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>2.74</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>7.32</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>8.15</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>12.94</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5.56</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>1.63</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2.17</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>10.59</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>3.38</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5.56</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>8.15</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>7.32</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>7.32</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>1.43</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5.87</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>3.56</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>10.59</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>2.74</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>7.32</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>6.21</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>11.72</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>1.04</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>3.38</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>8.15</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>7.32</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>6.93</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>10.06</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>3.38</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>4.4400000000000004</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>3.56</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>2.08</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>5.87</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>2.37</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>3.56</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>10.59</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>2.74</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>4.4400000000000004</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>10.59</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>7.32</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>7.32</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>5.87</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>1.63</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>3.56</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>2.74</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>3.37</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>8.15</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>9.5500000000000007</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>1.43</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>7.73</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>3.76</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>8.6</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>3.56</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>4.4400000000000004</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>7.32</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8C7A-4347-BDA9-5988915E448E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1492312976"/>
+        <c:axId val="1492150864"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1492312976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1492150864"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1492150864"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1492312976"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1910,6 +3201,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2942,20 +4273,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>565150</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>483870</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>154940</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>102870</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2982,16 +4829,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>28864</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>48490</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>472209</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>142701</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>444500</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>90053</xdr:rowOff>
+      <xdr:colOff>64885</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>184265</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3011,6 +4858,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>267229</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>96838</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>694090</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>177</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6A9D0EB-1367-ED55-E4F8-72E35C89F21A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3336,1367 +5219,1358 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CBDF5C0-C2D6-C34F-948D-E3962EE4D55E}">
-  <dimension ref="A1:G161"/>
+  <dimension ref="B1:G161"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>-0.7</v>
-      </c>
+    </row>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B2">
         <v>10.7</v>
       </c>
       <c r="C2">
+        <v>-0.7</v>
+      </c>
+      <c r="E2">
+        <v>-1.23</v>
+      </c>
+      <c r="F2">
         <v>9.5500000000000007</v>
       </c>
-      <c r="D2">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>-0.98</v>
-      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>9.1999999999999993</v>
       </c>
       <c r="C3">
+        <v>-0.98</v>
+      </c>
+      <c r="E3">
+        <v>-1.24</v>
+      </c>
+      <c r="F3">
         <v>4.2</v>
       </c>
-      <c r="D3">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>-1.37</v>
-      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>11.7</v>
       </c>
       <c r="C4">
+        <v>-1.37</v>
+      </c>
+      <c r="E4">
+        <v>-0.59</v>
+      </c>
+      <c r="F4">
         <v>2.08</v>
       </c>
-      <c r="D4">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>-1.74</v>
-      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>12.6</v>
       </c>
       <c r="C5">
+        <v>-1.74</v>
+      </c>
+      <c r="E5">
+        <v>-1.1299999999999999</v>
+      </c>
+      <c r="F5">
         <v>7.73</v>
       </c>
-      <c r="D5">
-        <v>-1.1299999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>-1.99</v>
-      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>11.2</v>
       </c>
       <c r="C6">
+        <v>-1.99</v>
+      </c>
+      <c r="E6">
+        <v>-0.86</v>
+      </c>
+      <c r="F6">
         <v>1.73</v>
       </c>
-      <c r="D6">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>-0.61</v>
-      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>4.9000000000000004</v>
       </c>
       <c r="C7">
+        <v>-0.61</v>
+      </c>
+      <c r="E7">
+        <v>-1.28</v>
+      </c>
+      <c r="F7">
         <v>7.73</v>
       </c>
-      <c r="D7">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>-0.33</v>
-      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>2.8</v>
       </c>
       <c r="C8">
+        <v>-0.33</v>
+      </c>
+      <c r="E8">
+        <v>-0.91</v>
+      </c>
+      <c r="F8">
         <v>2.74</v>
       </c>
-      <c r="D8">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>-0.47</v>
-      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>6.3</v>
       </c>
       <c r="C9">
+        <v>-0.47</v>
+      </c>
+      <c r="E9">
+        <v>-1.01</v>
+      </c>
+      <c r="F9">
         <v>3.04</v>
       </c>
-      <c r="D9">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>-0.26</v>
-      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>7.2</v>
       </c>
       <c r="C10">
+        <v>-0.26</v>
+      </c>
+      <c r="E10">
+        <v>-1.21</v>
+      </c>
+      <c r="F10">
         <v>6.56</v>
       </c>
-      <c r="D10">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>-0.15</v>
-      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>6.3</v>
       </c>
       <c r="C11">
+        <v>-0.15</v>
+      </c>
+      <c r="E11">
+        <v>-1.26</v>
+      </c>
+      <c r="F11">
         <v>6.93</v>
       </c>
-      <c r="D11">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>-0.3</v>
-      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>4</v>
       </c>
       <c r="C12">
+        <v>-0.3</v>
+      </c>
+      <c r="E12">
+        <v>-1.31</v>
+      </c>
+      <c r="F12">
         <v>10.06</v>
       </c>
-      <c r="D12">
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="E13">
+        <v>-0.71</v>
+      </c>
+      <c r="F13">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="E14">
+        <v>-0.75</v>
+      </c>
+      <c r="F14">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="E15">
+        <v>-1.23</v>
+      </c>
+      <c r="F15">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="E16">
+        <v>-0.71</v>
+      </c>
+      <c r="F16">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E17">
+        <v>-1.3</v>
+      </c>
+      <c r="F17">
+        <v>6.21</v>
+      </c>
+    </row>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E18">
+        <v>-1</v>
+      </c>
+      <c r="F18">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E19">
+        <v>-1.26</v>
+      </c>
+      <c r="F19">
+        <v>6.93</v>
+      </c>
+    </row>
+    <row r="20" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <v>-1.2</v>
+      </c>
+      <c r="F20">
+        <v>6.21</v>
+      </c>
+    </row>
+    <row r="21" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E21">
+        <v>-1.43</v>
+      </c>
+      <c r="F21">
+        <v>11.72</v>
+      </c>
+    </row>
+    <row r="22" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E22">
+        <v>-1.23</v>
+      </c>
+      <c r="F22">
+        <v>9.5500000000000007</v>
+      </c>
+    </row>
+    <row r="23" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E23">
+        <v>-0.94</v>
+      </c>
+      <c r="F23">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="24" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E24">
+        <v>-0.87</v>
+      </c>
+      <c r="F24">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="25" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E25">
+        <v>-1.23</v>
+      </c>
+      <c r="F25">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="26" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E26">
+        <v>-0.94</v>
+      </c>
+      <c r="F26">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="27" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E27">
+        <v>-1.21</v>
+      </c>
+      <c r="F27">
+        <v>4.4400000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E28">
+        <v>-1.03</v>
+      </c>
+      <c r="F28">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="29" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E29">
+        <v>-1.21</v>
+      </c>
+      <c r="F29">
+        <v>9.07</v>
+      </c>
+    </row>
+    <row r="30" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E30">
+        <v>-1.24</v>
+      </c>
+      <c r="F30">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="31" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E31">
+        <v>-1.1599999999999999</v>
+      </c>
+      <c r="F31">
+        <v>9.07</v>
+      </c>
+    </row>
+    <row r="32" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E32">
+        <v>-1.28</v>
+      </c>
+      <c r="F32">
+        <v>9.5500000000000007</v>
+      </c>
+    </row>
+    <row r="33" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E33">
+        <v>-1.05</v>
+      </c>
+      <c r="F33">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="34" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E34">
+        <v>-0.93</v>
+      </c>
+      <c r="F34">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="35" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E35">
+        <v>-1.18</v>
+      </c>
+      <c r="F35">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="36" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E36">
+        <v>-1.05</v>
+      </c>
+      <c r="F36">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="37" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E37">
+        <v>-1.4</v>
+      </c>
+      <c r="F37">
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="38" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E38">
+        <v>-0.93</v>
+      </c>
+      <c r="F38">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="39" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E39">
+        <v>-1.21</v>
+      </c>
+      <c r="F39">
+        <v>6.93</v>
+      </c>
+    </row>
+    <row r="40" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E40">
+        <v>-1.5</v>
+      </c>
+      <c r="F40">
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="41" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E41">
+        <v>-1.26</v>
+      </c>
+      <c r="F41">
+        <v>9.07</v>
+      </c>
+    </row>
+    <row r="42" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E42">
+        <v>-1.33</v>
+      </c>
+      <c r="F42">
+        <v>9.5500000000000007</v>
+      </c>
+    </row>
+    <row r="43" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E43">
         <v>-1.31</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C13">
+      <c r="F43">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="44" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E44">
+        <v>-0.74</v>
+      </c>
+      <c r="F44">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="45" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E45">
+        <v>-1.23</v>
+      </c>
+      <c r="F45">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="46" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E46">
+        <v>-1.31</v>
+      </c>
+      <c r="F46">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="47" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E47">
+        <v>-1.29</v>
+      </c>
+      <c r="F47">
         <v>5.87</v>
       </c>
-      <c r="D13">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C14">
-        <v>1.92</v>
-      </c>
-      <c r="D14">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C15">
+    </row>
+    <row r="48" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E48">
+        <v>-0.91</v>
+      </c>
+      <c r="F48">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="49" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E49">
+        <v>-1.27</v>
+      </c>
+      <c r="F49">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="50" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E50">
+        <v>-1.92</v>
+      </c>
+      <c r="F50">
+        <v>13.59</v>
+      </c>
+    </row>
+    <row r="51" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E51">
+        <v>-1.23</v>
+      </c>
+      <c r="F51">
         <v>7.73</v>
       </c>
-      <c r="D15">
+    </row>
+    <row r="52" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E52">
+        <v>-1.27</v>
+      </c>
+      <c r="F52">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="53" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E53">
+        <v>-1.48</v>
+      </c>
+      <c r="F53">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="54" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E54">
+        <v>-0.65</v>
+      </c>
+      <c r="F54">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="55" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E55">
         <v>-1.23</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C16">
+      <c r="F55">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="56" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E56">
+        <v>-0.87</v>
+      </c>
+      <c r="F56">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="57" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E57">
+        <v>-1.45</v>
+      </c>
+      <c r="F57">
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="58" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E58">
+        <v>-0.84</v>
+      </c>
+      <c r="F58">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="59" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E59">
+        <v>-1.1599999999999999</v>
+      </c>
+      <c r="F59">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="60" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E60">
+        <v>-1.29</v>
+      </c>
+      <c r="F60">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="61" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E61">
+        <v>-1.26</v>
+      </c>
+      <c r="F61">
+        <v>9.07</v>
+      </c>
+    </row>
+    <row r="62" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E62">
+        <v>-1.28</v>
+      </c>
+      <c r="F62">
+        <v>9.5500000000000007</v>
+      </c>
+    </row>
+    <row r="63" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E63">
+        <v>-1.39</v>
+      </c>
+      <c r="F63">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="64" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E64">
+        <v>-0.77</v>
+      </c>
+      <c r="F64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E65">
+        <v>-1.31</v>
+      </c>
+      <c r="F65">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="66" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E66">
+        <v>-1.01</v>
+      </c>
+      <c r="F66">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="67" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E67">
+        <v>-1.34</v>
+      </c>
+      <c r="F67">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="68" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E68">
+        <v>-1.18</v>
+      </c>
+      <c r="F68">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="69" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E69">
+        <v>-1.21</v>
+      </c>
+      <c r="F69">
+        <v>6.93</v>
+      </c>
+    </row>
+    <row r="70" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E70">
+        <v>-1.18</v>
+      </c>
+      <c r="F70">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="71" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E71">
+        <v>-1.21</v>
+      </c>
+      <c r="F71">
+        <v>6.93</v>
+      </c>
+    </row>
+    <row r="72" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E72">
+        <v>-1.18</v>
+      </c>
+      <c r="F72">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="73" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E73">
+        <v>-1.31</v>
+      </c>
+      <c r="F73">
+        <v>4.4400000000000004</v>
+      </c>
+    </row>
+    <row r="74" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E74">
+        <v>-0.84</v>
+      </c>
+      <c r="F74">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="75" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E75">
+        <v>-1.18</v>
+      </c>
+      <c r="F75">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="76" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E76">
+        <v>-1.23</v>
+      </c>
+      <c r="F76">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="77" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E77">
+        <v>-1.92</v>
+      </c>
+      <c r="F77">
+        <v>13.59</v>
+      </c>
+    </row>
+    <row r="78" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E78">
+        <v>-1.1399999999999999</v>
+      </c>
+      <c r="F78">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="79" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E79">
+        <v>-1.23</v>
+      </c>
+      <c r="F79">
+        <v>9.5549999999999997</v>
+      </c>
+    </row>
+    <row r="80" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E80">
+        <v>-1.34</v>
+      </c>
+      <c r="F80">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="81" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E81">
+        <v>-1.21</v>
+      </c>
+      <c r="F81">
+        <v>6.93</v>
+      </c>
+    </row>
+    <row r="82" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E82">
+        <v>-1.27</v>
+      </c>
+      <c r="F82">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="83" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E83">
+        <v>-1.32</v>
+      </c>
+      <c r="F83">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="84" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E84">
+        <v>-0.66</v>
+      </c>
+      <c r="F84">
         <v>1.73</v>
       </c>
-      <c r="D16">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C17">
+    </row>
+    <row r="85" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E85">
+        <v>-1.23</v>
+      </c>
+      <c r="F85">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="86" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E86">
+        <v>-1.05</v>
+      </c>
+      <c r="F86">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="87" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E87">
+        <v>-1.34</v>
+      </c>
+      <c r="F87">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="88" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E88">
+        <v>-0.96</v>
+      </c>
+      <c r="F88">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="89" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E89">
+        <v>-1.27</v>
+      </c>
+      <c r="F89">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="90" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E90">
+        <v>-1.34</v>
+      </c>
+      <c r="F90">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="91" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E91">
+        <v>-1.75</v>
+      </c>
+      <c r="F91">
+        <v>12.94</v>
+      </c>
+    </row>
+    <row r="92" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E92">
+        <v>-1.22</v>
+      </c>
+      <c r="F92">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="93" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E93">
+        <v>-1.48</v>
+      </c>
+      <c r="F93">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="94" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E94">
+        <v>-0.69</v>
+      </c>
+      <c r="F94">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="95" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E95">
+        <v>-1.28</v>
+      </c>
+      <c r="F95">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="96" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E96">
+        <v>-0.96</v>
+      </c>
+      <c r="F96">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="97" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E97">
+        <v>-1.45</v>
+      </c>
+      <c r="F97">
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="98" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E98">
+        <v>-1.05</v>
+      </c>
+      <c r="F98">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="99" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E99">
+        <v>-1.17</v>
+      </c>
+      <c r="F99">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="100" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E100">
+        <v>-1.29</v>
+      </c>
+      <c r="F100">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="101" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E101">
+        <v>-1.27</v>
+      </c>
+      <c r="F101">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="102" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E102">
+        <v>-1.27</v>
+      </c>
+      <c r="F102">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="103" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E103">
+        <v>-1.43</v>
+      </c>
+      <c r="F103">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="104" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E104">
+        <v>-0.64</v>
+      </c>
+      <c r="F104">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="105" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E105">
+        <v>-1.19</v>
+      </c>
+      <c r="F105">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="106" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E106">
+        <v>-1.08</v>
+      </c>
+      <c r="F106">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="107" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E107">
+        <v>-1.45</v>
+      </c>
+      <c r="F107">
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="108" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E108">
+        <v>-0.91</v>
+      </c>
+      <c r="F108">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="109" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E109">
+        <v>-1.17</v>
+      </c>
+      <c r="F109">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="110" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E110">
+        <v>-1.25</v>
+      </c>
+      <c r="F110">
         <v>6.21</v>
       </c>
-      <c r="D17">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C18">
+    </row>
+    <row r="111" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E111">
+        <v>-1.53</v>
+      </c>
+      <c r="F111">
+        <v>11.72</v>
+      </c>
+    </row>
+    <row r="112" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E112">
+        <v>-1.18</v>
+      </c>
+      <c r="F112">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="113" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E113">
+        <v>-1.38</v>
+      </c>
+      <c r="F113">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="114" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E114">
+        <v>-0.63</v>
+      </c>
+      <c r="F114">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="115" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E115">
+        <v>-1.18</v>
+      </c>
+      <c r="F115">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="116" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E116">
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="F116">
         <v>3.38</v>
       </c>
-      <c r="D18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C19">
+    </row>
+    <row r="117" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E117">
+        <v>-1.29</v>
+      </c>
+      <c r="F117">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="118" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E118">
+        <v>-0.98</v>
+      </c>
+      <c r="F118">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="119" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E119">
+        <v>-1.17</v>
+      </c>
+      <c r="F119">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="120" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E120">
+        <v>-1.18</v>
+      </c>
+      <c r="F120">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="121" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E121">
+        <v>-1.1599999999999999</v>
+      </c>
+      <c r="F121">
         <v>6.93</v>
       </c>
-      <c r="D19">
+    </row>
+    <row r="122" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E122">
         <v>-1.26</v>
       </c>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C20">
-        <v>6.21</v>
-      </c>
-      <c r="D20">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C21">
-        <v>11.72</v>
-      </c>
-      <c r="D21">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C22">
-        <v>9.5500000000000007</v>
-      </c>
-      <c r="D22">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C23">
-        <v>2.61</v>
-      </c>
-      <c r="D23">
-        <v>-0.94</v>
-      </c>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C24">
-        <v>2.48</v>
-      </c>
-      <c r="D24">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C25">
+      <c r="F122">
+        <v>10.06</v>
+      </c>
+    </row>
+    <row r="123" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E123">
+        <v>-1.38</v>
+      </c>
+      <c r="F123">
         <v>7.73</v>
       </c>
-      <c r="D25">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C26">
-        <v>2.61</v>
-      </c>
-      <c r="D26">
-        <v>-0.94</v>
-      </c>
-    </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C27">
+    </row>
+    <row r="124" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E124">
+        <v>-0.95</v>
+      </c>
+      <c r="F124">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="125" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E125">
+        <v>-1.06</v>
+      </c>
+      <c r="F125">
         <v>4.4400000000000004</v>
       </c>
-      <c r="D27">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C28">
+    </row>
+    <row r="126" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E126">
+        <v>-1.03</v>
+      </c>
+      <c r="F126">
         <v>3.56</v>
       </c>
-      <c r="D28">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C29">
-        <v>9.07</v>
-      </c>
-      <c r="D29">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C30">
-        <v>8.15</v>
-      </c>
-      <c r="D30">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C31">
-        <v>9.07</v>
-      </c>
-      <c r="D31">
-        <v>-1.1599999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C32">
-        <v>9.5500000000000007</v>
-      </c>
-      <c r="D32">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C33">
-        <v>3.38</v>
-      </c>
-      <c r="D33">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C34">
-        <v>2.27</v>
-      </c>
-      <c r="D34">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C35">
-        <v>7.73</v>
-      </c>
-      <c r="D35">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C36">
-        <v>3.37</v>
-      </c>
-      <c r="D36">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C37">
-        <v>10.59</v>
-      </c>
-      <c r="D37">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C38">
-        <v>3.2</v>
-      </c>
-      <c r="D38">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C39">
-        <v>6.93</v>
-      </c>
-      <c r="D39">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C40">
-        <v>10.59</v>
-      </c>
-      <c r="D40">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C41">
-        <v>9.07</v>
-      </c>
-      <c r="D41">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C42">
-        <v>9.5500000000000007</v>
-      </c>
-      <c r="D42">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C43">
-        <v>5.26</v>
-      </c>
-      <c r="D43">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C44">
-        <v>2.08</v>
-      </c>
-      <c r="D44">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C45">
-        <v>7.73</v>
-      </c>
-      <c r="D45">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C46">
-        <v>5.26</v>
-      </c>
-      <c r="D46">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C47">
-        <v>5.87</v>
-      </c>
-      <c r="D47">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C48">
-        <v>2.17</v>
-      </c>
-      <c r="D48">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C49">
-        <v>7.32</v>
-      </c>
-      <c r="D49">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C50">
-        <v>13.59</v>
-      </c>
-      <c r="D50">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C51">
-        <v>7.73</v>
-      </c>
-      <c r="D51">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C52">
-        <v>7.32</v>
-      </c>
-      <c r="D52">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C53">
-        <v>7.73</v>
-      </c>
-      <c r="D53">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C54">
-        <v>1.47</v>
-      </c>
-      <c r="D54">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C55">
-        <v>7.73</v>
-      </c>
-      <c r="D55">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C56">
-        <v>1.54</v>
-      </c>
-      <c r="D56">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C57">
-        <v>10.59</v>
-      </c>
-      <c r="D57">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C58">
-        <v>2.08</v>
-      </c>
-      <c r="D58">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C59">
-        <v>5.26</v>
-      </c>
-      <c r="D59">
-        <v>-1.1599999999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C60">
-        <v>8.15</v>
-      </c>
-      <c r="D60">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C61">
-        <v>9.07</v>
-      </c>
-      <c r="D61">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C62">
-        <v>9.5500000000000007</v>
-      </c>
-      <c r="D62">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C63">
-        <v>5.89</v>
-      </c>
-      <c r="D63">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C64">
-        <v>2</v>
-      </c>
-      <c r="D64">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C65">
-        <v>10.6</v>
-      </c>
-      <c r="D65">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C66">
-        <v>2.17</v>
-      </c>
-      <c r="D66">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C67">
-        <v>8.15</v>
-      </c>
-      <c r="D67">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C68">
-        <v>4.7</v>
-      </c>
-      <c r="D68">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C69">
-        <v>6.93</v>
-      </c>
-      <c r="D69">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C70">
-        <v>4.7</v>
-      </c>
-      <c r="D70">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C71">
-        <v>6.93</v>
-      </c>
-      <c r="D71">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C72">
-        <v>7.73</v>
-      </c>
-      <c r="D72">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C73">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="D73">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C74">
-        <v>1.85</v>
-      </c>
-      <c r="D74">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C75">
-        <v>7.73</v>
-      </c>
-      <c r="D75">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C76">
-        <v>3.56</v>
-      </c>
-      <c r="D76">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C77">
-        <v>13.59</v>
-      </c>
-      <c r="D77">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C78">
-        <v>4.2</v>
-      </c>
-      <c r="D78">
-        <v>-1.1399999999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C79">
-        <v>9.5549999999999997</v>
-      </c>
-      <c r="D79">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="80" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C80">
-        <v>8.15</v>
-      </c>
-      <c r="D80">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="81" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C81">
-        <v>6.93</v>
-      </c>
-      <c r="D81">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="82" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C82">
-        <v>7.32</v>
-      </c>
-      <c r="D82">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="83" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C83">
-        <v>7.32</v>
-      </c>
-      <c r="D83">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="84" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C84">
-        <v>1.73</v>
-      </c>
-      <c r="D84">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="85" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C85">
-        <v>7.73</v>
-      </c>
-      <c r="D85">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="86" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C86">
-        <v>3.38</v>
-      </c>
-      <c r="D86">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="87" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C87">
-        <v>8.15</v>
-      </c>
-      <c r="D87">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="88" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C88">
-        <v>2.74</v>
-      </c>
-      <c r="D88">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="89" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C89">
-        <v>7.32</v>
-      </c>
-      <c r="D89">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="90" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C90">
-        <v>8.15</v>
-      </c>
-      <c r="D90">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="91" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C91">
-        <v>12.94</v>
-      </c>
-      <c r="D91">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="92" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C92">
-        <v>5.56</v>
-      </c>
-      <c r="D92">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="93" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C93">
-        <v>7.73</v>
-      </c>
-      <c r="D93">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="94" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C94">
-        <v>1.63</v>
-      </c>
-      <c r="D94">
-        <v>-0.69</v>
-      </c>
-    </row>
-    <row r="95" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C95">
-        <v>7.73</v>
-      </c>
-      <c r="D95">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="96" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C96">
-        <v>2.17</v>
-      </c>
-      <c r="D96">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="97" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C97">
-        <v>10.59</v>
-      </c>
-      <c r="D97">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="98" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C98">
-        <v>3.38</v>
-      </c>
-      <c r="D98">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="99" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C99">
-        <v>5.56</v>
-      </c>
-      <c r="D99">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="100" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C100">
-        <v>8.15</v>
-      </c>
-      <c r="D100">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="101" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C101">
-        <v>7.32</v>
-      </c>
-      <c r="D101">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="102" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C102">
-        <v>7.32</v>
-      </c>
-      <c r="D102">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="103" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C103">
-        <v>7.73</v>
-      </c>
-      <c r="D103">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="104" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C104">
-        <v>1.43</v>
-      </c>
-      <c r="D104">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="105" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C105">
-        <v>5.87</v>
-      </c>
-      <c r="D105">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="106" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C106">
-        <v>3.56</v>
-      </c>
-      <c r="D106">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="107" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C107">
-        <v>10.59</v>
-      </c>
-      <c r="D107">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="108" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C108">
-        <v>2.74</v>
-      </c>
-      <c r="D108">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="109" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C109">
-        <v>7.32</v>
-      </c>
-      <c r="D109">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="110" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C110">
-        <v>6.21</v>
-      </c>
-      <c r="D110">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="111" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C111">
-        <v>11.72</v>
-      </c>
-      <c r="D111">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="112" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C112">
-        <v>7.73</v>
-      </c>
-      <c r="D112">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="113" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C113">
-        <v>7.73</v>
-      </c>
-      <c r="D113">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="114" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C114">
-        <v>1.04</v>
-      </c>
-      <c r="D114">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="115" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C115">
-        <v>7.73</v>
-      </c>
-      <c r="D115">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="116" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C116">
-        <v>3.38</v>
-      </c>
-      <c r="D116">
-        <v>-1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="117" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C117">
-        <v>8.15</v>
-      </c>
-      <c r="D117">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="118" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C118">
-        <v>3.2</v>
-      </c>
-      <c r="D118">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="119" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C119">
-        <v>7.32</v>
-      </c>
-      <c r="D119">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="120" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C120">
-        <v>4.7</v>
-      </c>
-      <c r="D120">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="121" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C121">
-        <v>6.93</v>
-      </c>
-      <c r="D121">
-        <v>-1.1599999999999999</v>
-      </c>
-    </row>
-    <row r="122" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C122">
-        <v>10.06</v>
-      </c>
-      <c r="D122">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="123" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C123">
-        <v>7.73</v>
-      </c>
-      <c r="D123">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="124" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C124">
-        <v>3.38</v>
-      </c>
-      <c r="D124">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="125" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C125">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="D125">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="126" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C126">
-        <v>3.56</v>
-      </c>
-      <c r="D126">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="127" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="F127" t="s">
-        <v>2</v>
-      </c>
+    </row>
+    <row r="127" spans="5:7" x14ac:dyDescent="0.2">
       <c r="G127">
         <v>8.15</v>
       </c>
     </row>
-    <row r="128" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C128">
+    <row r="128" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E128">
+        <v>-0.79</v>
+      </c>
+      <c r="F128">
         <v>2.08</v>
       </c>
-      <c r="D128">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="129" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C129">
+    </row>
+    <row r="129" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E129">
+        <v>-1.1299999999999999</v>
+      </c>
+      <c r="F129">
         <v>4.7</v>
       </c>
-      <c r="D129">
-        <v>-1.1299999999999999</v>
-      </c>
-    </row>
-    <row r="130" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C130">
+    </row>
+    <row r="130" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E130">
+        <v>-1.08</v>
+      </c>
+      <c r="F130">
         <v>3.2</v>
       </c>
-      <c r="D130">
+    </row>
+    <row r="131" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E131">
+        <v>-1.28</v>
+      </c>
+      <c r="F131">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="132" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E132">
+        <v>-1.18</v>
+      </c>
+      <c r="F132">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="133" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E133">
+        <v>-1.39</v>
+      </c>
+      <c r="F133">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="134" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E134">
+        <v>-0.85</v>
+      </c>
+      <c r="F134">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="135" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E135">
+        <v>-1.18</v>
+      </c>
+      <c r="F135">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="136" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E136">
         <v>-1.08</v>
       </c>
-    </row>
-    <row r="131" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C131">
+      <c r="F136">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="137" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E137">
+        <v>-1.4</v>
+      </c>
+      <c r="F137">
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="138" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E138">
+        <v>-0.91</v>
+      </c>
+      <c r="F138">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="139" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E139">
+        <v>-1.1599999999999999</v>
+      </c>
+      <c r="F139">
+        <v>4.4400000000000004</v>
+      </c>
+    </row>
+    <row r="140" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E140">
+        <v>-1.45</v>
+      </c>
+      <c r="F140">
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="141" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E141">
+        <v>-1.22</v>
+      </c>
+      <c r="F141">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="142" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E142">
+        <v>-1.17</v>
+      </c>
+      <c r="F142">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="143" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E143">
+        <v>-1.39</v>
+      </c>
+      <c r="F143">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="144" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E144">
+        <v>-0.69</v>
+      </c>
+      <c r="F144">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="145" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E145">
+        <v>-1.23</v>
+      </c>
+      <c r="F145">
         <v>7.73</v>
       </c>
-      <c r="D131">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="132" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C132">
-        <v>7.73</v>
-      </c>
-      <c r="D132">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="133" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C133">
-        <v>5.87</v>
-      </c>
-      <c r="D133">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="134" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C134">
-        <v>2.37</v>
-      </c>
-      <c r="D134">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="135" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C135">
-        <v>7.73</v>
-      </c>
-      <c r="D135">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="136" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C136">
+    </row>
+    <row r="146" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E146">
+        <v>-1.08</v>
+      </c>
+      <c r="F146">
         <v>3.56</v>
       </c>
-      <c r="D136">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="137" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C137">
-        <v>10.59</v>
-      </c>
-      <c r="D137">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="138" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C138">
-        <v>2.74</v>
-      </c>
-      <c r="D138">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="139" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C139">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="D139">
-        <v>-1.1599999999999999</v>
-      </c>
-    </row>
-    <row r="140" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C140">
-        <v>10.59</v>
-      </c>
-      <c r="D140">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="141" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C141">
-        <v>7.32</v>
-      </c>
-      <c r="D141">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="142" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C142">
-        <v>7.32</v>
-      </c>
-      <c r="D142">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="143" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C143">
-        <v>5.87</v>
-      </c>
-      <c r="D143">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="144" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C144">
-        <v>1.63</v>
-      </c>
-      <c r="D144">
-        <v>-0.69</v>
-      </c>
-    </row>
-    <row r="145" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C145">
-        <v>7.73</v>
-      </c>
-      <c r="D145">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="146" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C146">
-        <v>3.56</v>
-      </c>
-      <c r="D146">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="147" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="F147" t="s">
-        <v>2</v>
-      </c>
+    </row>
+    <row r="147" spans="5:7" x14ac:dyDescent="0.2">
       <c r="G147">
         <v>11.15</v>
       </c>
     </row>
-    <row r="148" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C148">
+    <row r="148" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E148">
+        <v>-0.91</v>
+      </c>
+      <c r="F148">
         <v>2.74</v>
       </c>
-      <c r="D148">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="149" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C149">
+    </row>
+    <row r="149" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E149">
+        <v>-1</v>
+      </c>
+      <c r="F149">
         <v>3.37</v>
       </c>
-      <c r="D149">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="150" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C150">
+    </row>
+    <row r="150" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E150">
+        <v>-1.29</v>
+      </c>
+      <c r="F150">
         <v>8.15</v>
       </c>
-      <c r="D150">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="151" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C151">
+    </row>
+    <row r="151" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E151">
+        <v>-1.33</v>
+      </c>
+      <c r="F151">
         <v>9.5500000000000007</v>
       </c>
-      <c r="D151">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="152" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C152">
+    </row>
+    <row r="152" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E152">
+        <v>-1.18</v>
+      </c>
+      <c r="F152">
         <v>7.73</v>
       </c>
-      <c r="D152">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="153" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C153">
+    </row>
+    <row r="153" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E153">
+        <v>-1.43</v>
+      </c>
+      <c r="F153">
         <v>7.73</v>
       </c>
-      <c r="D153">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="154" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C154">
+    </row>
+    <row r="154" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E154">
+        <v>-0.69</v>
+      </c>
+      <c r="F154">
         <v>1.43</v>
       </c>
-      <c r="D154">
-        <v>-0.69</v>
-      </c>
-    </row>
-    <row r="155" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C155">
+    </row>
+    <row r="155" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E155">
+        <v>-1.28</v>
+      </c>
+      <c r="F155">
         <v>7.73</v>
       </c>
-      <c r="D155">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="156" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C156">
+    </row>
+    <row r="156" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E156">
+        <v>-1.3</v>
+      </c>
+      <c r="F156">
         <v>3.76</v>
       </c>
-      <c r="D156">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="157" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C157">
+    </row>
+    <row r="157" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E157">
+        <v>-1.45</v>
+      </c>
+      <c r="F157">
         <v>8.6</v>
       </c>
-      <c r="D157">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="158" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C158">
+    </row>
+    <row r="158" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E158">
+        <v>-1.03</v>
+      </c>
+      <c r="F158">
         <v>3.56</v>
       </c>
-      <c r="D158">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="159" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C159">
+    </row>
+    <row r="159" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E159">
+        <v>-1.1100000000000001</v>
+      </c>
+      <c r="F159">
         <v>4.4400000000000004</v>
       </c>
-      <c r="D159">
-        <v>-1.1100000000000001</v>
-      </c>
-    </row>
-    <row r="160" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="F160" t="s">
-        <v>2</v>
-      </c>
+    </row>
+    <row r="160" spans="5:7" x14ac:dyDescent="0.2">
       <c r="G160">
         <v>8.15</v>
       </c>
     </row>
-    <row r="161" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C161">
+    <row r="161" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E161">
+        <v>-1.22</v>
+      </c>
+      <c r="F161">
         <v>7.32</v>
-      </c>
-      <c r="D161">
-        <v>-1.22</v>
       </c>
     </row>
   </sheetData>
